--- a/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/outputs/history/composite_coefficients.xlsx
+++ b/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/outputs/history/composite_coefficients.xlsx
@@ -564,9 +564,9 @@
     <col min="1" max="1" width="12.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="23.7109375" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="6" customWidth="1"/>
-    <col min="6" max="7" width="23.7109375" style="6" customWidth="1"/>
+    <col min="4" max="5" width="25.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="24" customHeight="1">
@@ -600,19 +600,19 @@
         <v>0.008933463928001794</v>
       </c>
       <c r="C2" s="5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D2" s="6">
-        <v>-0.000412905506504816</v>
+        <v>-4.715217285070421E-05</v>
       </c>
       <c r="E2" s="6">
-        <v>0.0004376965806218493</v>
+        <v>1.679394465405647E-05</v>
       </c>
       <c r="F2" s="6">
-        <v>0.0006204916746924984</v>
+        <v>6.851059154904521E-05</v>
       </c>
       <c r="G2" s="6">
-        <v>0.00171206970073486</v>
+        <v>7.850860839819569E-05</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -623,19 +623,19 @@
         <v>0.006988256885576944</v>
       </c>
       <c r="C3" s="5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D3" s="6">
-        <v>-0.0004469541440885421</v>
+        <v>-5.120792016205312E-05</v>
       </c>
       <c r="E3" s="6">
-        <v>0.0003719356578803985</v>
+        <v>1.603885648314681E-05</v>
       </c>
       <c r="F3" s="6">
-        <v>0.0005492304021921092</v>
+        <v>6.128668276591203E-05</v>
       </c>
       <c r="G3" s="6">
-        <v>0.001648704852962201</v>
+        <v>8.136944009559559E-05</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -646,19 +646,19 @@
         <v>0.007267835726339065</v>
       </c>
       <c r="C4" s="5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D4" s="6">
-        <v>-0.0002433675652166297</v>
+        <v>-2.79730617492962E-05</v>
       </c>
       <c r="E4" s="6">
-        <v>0.0004094445988108191</v>
+        <v>1.018724278205241E-05</v>
       </c>
       <c r="F4" s="6">
-        <v>0.0003565855311118803</v>
+        <v>3.871180993045113E-05</v>
       </c>
       <c r="G4" s="6">
-        <v>0.001566960878844376</v>
+        <v>7.957124324169164E-05</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -669,19 +669,19 @@
         <v>0.006346243995864018</v>
       </c>
       <c r="C5" s="5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D5" s="6">
-        <v>-0.0002221877073997549</v>
+        <v>-2.583560547088646E-05</v>
       </c>
       <c r="E5" s="6">
-        <v>0.0004185667073522025</v>
+        <v>-8.267976859809881E-06</v>
       </c>
       <c r="F5" s="6">
-        <v>0.0005678284402463072</v>
+        <v>6.458663359428557E-05</v>
       </c>
       <c r="G5" s="6">
-        <v>0.001705936495217238</v>
+        <v>9.059029438561751E-05</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -692,19 +692,19 @@
         <v>0.005735339187991334</v>
       </c>
       <c r="C6" s="5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D6" s="6">
-        <v>-0.0001517395185625265</v>
+        <v>-1.792548057100276E-05</v>
       </c>
       <c r="E6" s="6">
-        <v>0.0003743010935211442</v>
+        <v>-3.616934919099556E-06</v>
       </c>
       <c r="F6" s="6">
-        <v>0.0006534639008719712</v>
+        <v>7.560473428845272E-05</v>
       </c>
       <c r="G6" s="6">
-        <v>0.001758763225408429</v>
+        <v>0.0001000224538000039</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -715,19 +715,19 @@
         <v>0.004486179247618815</v>
       </c>
       <c r="C7" s="5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D7" s="6">
-        <v>-0.0001301487420422628</v>
+        <v>-1.616107947159149E-05</v>
       </c>
       <c r="E7" s="6">
-        <v>0.0003066967438321626</v>
+        <v>1.477857799533095E-06</v>
       </c>
       <c r="F7" s="6">
-        <v>0.000967260255786835</v>
+        <v>0.000116804422405274</v>
       </c>
       <c r="G7" s="6">
-        <v>0.001812665550796823</v>
+        <v>9.767131371843087E-05</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -738,19 +738,19 @@
         <v>0.002627892235804006</v>
       </c>
       <c r="C8" s="5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D8" s="6">
-        <v>-0.0003232565467824077</v>
+        <v>-3.888193844128317E-05</v>
       </c>
       <c r="E8" s="6">
-        <v>0.0003251572571172175</v>
+        <v>5.95320262197559E-06</v>
       </c>
       <c r="F8" s="6">
-        <v>0.0008646986933253679</v>
+        <v>0.0001049156928105027</v>
       </c>
       <c r="G8" s="6">
-        <v>0.001834995040215628</v>
+        <v>0.0001082938553913588</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -761,19 +761,19 @@
         <v>0.002834920965610214</v>
       </c>
       <c r="C9" s="5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D9" s="6">
-        <v>-0.0003769366209056438</v>
+        <v>-4.809341925490164E-05</v>
       </c>
       <c r="E9" s="6">
-        <v>0.0001896927267804954</v>
+        <v>-1.091464427545526E-05</v>
       </c>
       <c r="F9" s="6">
-        <v>0.0007863468366880712</v>
+        <v>9.528136428970297E-05</v>
       </c>
       <c r="G9" s="6">
-        <v>0.00198862111772696</v>
+        <v>0.0001245772942974977</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -784,19 +784,19 @@
         <v>0.001089062058637795</v>
       </c>
       <c r="C10" s="5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D10" s="6">
-        <v>-0.0002198275987128443</v>
+        <v>-2.92432763359833E-05</v>
       </c>
       <c r="E10" s="6">
-        <v>0.0001324918938479957</v>
+        <v>-9.154816642855279E-06</v>
       </c>
       <c r="F10" s="6">
-        <v>0.0006677607739235746</v>
+        <v>8.137134852439235E-05</v>
       </c>
       <c r="G10" s="6">
-        <v>0.001960217222477849</v>
+        <v>0.0001315359724109073</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -807,19 +807,19 @@
         <v>0.001643278137273866</v>
       </c>
       <c r="C11" s="5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D11" s="6">
-        <v>-0.0001950071359168204</v>
+        <v>-2.713879672238644E-05</v>
       </c>
       <c r="E11" s="6">
-        <v>-6.842924054064925E-05</v>
+        <v>-2.513933395651017E-05</v>
       </c>
       <c r="F11" s="6">
-        <v>0.0006632776946515653</v>
+        <v>8.049502376339491E-05</v>
       </c>
       <c r="G11" s="6">
-        <v>0.002145389342264813</v>
+        <v>0.0001535085389088287</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -830,19 +830,19 @@
         <v>0.001366920466552098</v>
       </c>
       <c r="C12" s="5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D12" s="6">
-        <v>-4.967193892437569E-05</v>
+        <v>-9.932618340821456E-06</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.000118758053194215</v>
+        <v>-3.06674204741317E-05</v>
       </c>
       <c r="F12" s="6">
-        <v>0.0007309378925033376</v>
+        <v>9.034756899539601E-05</v>
       </c>
       <c r="G12" s="6">
-        <v>0.002105924732912734</v>
+        <v>0.0001624891783201663</v>
       </c>
     </row>
   </sheetData>
